--- a/voting/036_style_voting_form--voting.xlsx
+++ b/voting/036_style_voting_form--voting.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Form Category Input</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Form Date Input</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Form Time Input</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Form Email Input</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Form Phone Input</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_checkbox_range_choices</t>
+          <t>form_radios_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_checkbox_range_input_choices</t>
+          <t>form_checkbox_range_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1386,10 +1386,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>form_checkbox_range_input_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
